--- a/naver-place-crawler/results_health/옹진군_헬스장.xlsx
+++ b/naver-place-crawler/results_health/옹진군_헬스장.xlsx
@@ -427,7 +427,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="43" customWidth="1" min="7" max="7"/>
-    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="37" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>999</v>
+        <v>1003</v>
       </c>
       <c r="Q2" t="n">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="R2" t="n">
-        <v>1575</v>
+        <v>1581</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -646,7 +646,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1233</v>
+        <v>1245</v>
       </c>
       <c r="Q3" t="n">
-        <v>473</v>
+        <v>483</v>
       </c>
       <c r="R3" t="n">
-        <v>1706</v>
+        <v>1728</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>879</v>
+        <v>888</v>
       </c>
       <c r="Q4" t="n">
-        <v>452</v>
+        <v>476</v>
       </c>
       <c r="R4" t="n">
-        <v>1331</v>
+        <v>1364</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -834,37 +834,41 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>토크스퀘어</t>
+          <t>유티비티짐 24시</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>torquesquare@naver.com</t>
+          <t>utbt_gym@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0507-1335-6338</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천광역시 중구 영종대로 94 9층 토크스퀘어</t>
+          <t>인천광역시 중구 흰바위로 228 비전프라자 9층 유티비티짐</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/torquesquare</t>
+          <t>https://blog.naver.com/utbt_gym</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -899,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>240</v>
+        <v>1281</v>
       </c>
       <c r="Q5" t="n">
-        <v>663</v>
+        <v>271</v>
       </c>
       <c r="R5" t="n">
-        <v>903</v>
+        <v>1552</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -914,17 +918,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1814715870</t>
+          <t>1116960254</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1814715870</t>
+          <t>https://m.place.naver.com/place/1116960254</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -936,29 +940,25 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>더베럴캠프 그룹PT</t>
+          <t>토크스퀘어</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>thebetterfitness1@naver.com</t>
+          <t>torquesquare@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0507-1440-8974</t>
-        </is>
-      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘중앙로225번길 3 8층 803호</t>
+          <t>인천광역시 중구 영종대로 94 9층 토크스퀘어</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/thebetterfitness1</t>
+          <t>https://blog.naver.com/torquesquare</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -993,13 +993,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>26</v>
+        <v>240</v>
       </c>
       <c r="Q6" t="n">
-        <v>109</v>
+        <v>671</v>
       </c>
       <c r="R6" t="n">
-        <v>135</v>
+        <v>911</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1008,17 +1008,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1800815900</t>
+          <t>1814715870</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1800815900</t>
+          <t>https://m.place.naver.com/place/1814715870</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/옹진군_헬스장.xlsx
+++ b/naver-place-crawler/results_health/옹진군_헬스장.xlsx
@@ -591,17 +591,17 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>O</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -624,10 +624,10 @@
         <v>1003</v>
       </c>
       <c r="Q2" t="n">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="R2" t="n">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -903,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="Q5" t="n">
         <v>271</v>
       </c>
       <c r="R5" t="n">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>

--- a/naver-place-crawler/results_health/옹진군_헬스장.xlsx
+++ b/naver-place-crawler/results_health/옹진군_헬스장.xlsx
@@ -417,17 +417,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V6"/>
+  <dimension ref="A1:V63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="43" customWidth="1" min="7" max="7"/>
-    <col width="37" customWidth="1" min="8" max="8"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -559,34 +559,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>더베럴피트니스 헬스PT 영종도점</t>
+          <t>익스트림패션</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>thebetterfitness1@naver.com</t>
+          <t>place_simulation@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0507-1492-8972</t>
-        </is>
-      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘중앙로225번길 3 7층, 8층</t>
+          <t>인천광역시 강화군 강화읍 동문안길20번길 6</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://thebetterfitness.com</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,7 +592,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -617,17 +613,17 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1003</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>579</v>
+        <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>1582</v>
+        <v>1</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +632,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1062429885</t>
+          <t>1135791607</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1062429885</t>
+          <t>https://m.place.naver.com/place/1135791607</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -658,29 +654,25 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>찐피트니스 24시</t>
+          <t>에이스짐</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>zzin_fitness@naver.com</t>
+          <t>acegym2@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0507-1343-8596</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천광역시 중구 흰바위로 236 메가타워 10층</t>
+          <t>인천광역시 강화군 강화읍 강화대로404번길 7 3층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/zzin_fitness</t>
+          <t>https://instagram.com/ace__gym?igshid=ye2mgag95d7j</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -695,7 +687,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -715,13 +707,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1245</v>
+        <v>23</v>
       </c>
       <c r="Q3" t="n">
-        <v>483</v>
+        <v>15</v>
       </c>
       <c r="R3" t="n">
-        <v>1728</v>
+        <v>38</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,51 +722,51 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1224879470</t>
+          <t>1768451605</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1224879470</t>
+          <t>https://m.place.naver.com/place/1768451605</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>힙해짐 24시 헬스 PT 영종도점</t>
+          <t>토크짐 영종운서역점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>kwon56231@naver.com</t>
+          <t>dietdagym@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1439-0517</t>
+          <t>0507-1493-9876</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천광역시 중구 하늘별빛로65번길 21 701, 702, 703, 704호</t>
+          <t>인천광역시 중구 신도시남로 28 5층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/dietdagym</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -784,12 +776,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -809,13 +801,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>888</v>
+        <v>235</v>
       </c>
       <c r="Q4" t="n">
-        <v>476</v>
+        <v>346</v>
       </c>
       <c r="R4" t="n">
-        <v>1364</v>
+        <v>581</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,17 +816,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1731606747</t>
+          <t>1347888474</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1731606747</t>
+          <t>https://m.place.naver.com/place/1347888474</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -846,29 +838,25 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>유티비티짐 24시</t>
+          <t>ACE GYM</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>utbt_gym@naver.com</t>
+          <t>wsh09@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0507-1335-6338</t>
-        </is>
-      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천광역시 중구 흰바위로 228 비전프라자 9층 유티비티짐</t>
+          <t>인천광역시 강화군 강화읍 강화대로404번길 7</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/utbt_gym</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -878,12 +866,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -899,17 +887,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1282</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>271</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>1553</v>
+        <v>1</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,47 +906,51 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1116960254</t>
+          <t>1944033879</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1116960254</t>
+          <t>https://m.place.naver.com/place/1944033879</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>세탁소</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>토크스퀘어</t>
+          <t>수건세탁업체.세탁공장.미용실.헬스장.사우나.수건빨래.대량전문</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>torquesquare@naver.com</t>
+          <t>total_clean_laundry@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>070-4538-5722</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천광역시 중구 영종대로 94 9층 토크스퀘어</t>
+          <t>경기도 안산시 단원구 대부남동</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/torquesquare</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -968,12 +960,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -989,36 +981,5362 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>1831169611</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1831169611</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>공유누리 개방자원</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>영종지사 헬스장</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>koreaportalsite@naver.com</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>인천광역시 중구 영종대로196번길 15-21 (운서동) 한전 영종지사</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>1443743188</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1443743188</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>머슬카페 운서역 메가박스점</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>musclecafe@naver.com</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0507-1417-0850</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>인천광역시 중구 영종대로 184 영종예스타워복합상영관 6층 머슬카페 피트니스</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/musclecafe</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>239</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>42</v>
+      </c>
+      <c r="R8" t="n">
+        <v>281</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>1711611290</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1711611290</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>예스비피트니스</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>psb1433@naver.com</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0507-1337-1433</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>인천광역시 중구 햇내로28번길 10 더예스클라우드 A동 2층 204, 205호</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/psb1433</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>15</v>
+      </c>
+      <c r="R9" t="n">
+        <v>22</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>1578271523</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1578271523</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>GYM201</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>bricks_gym@naver.com</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0507-1368-2028</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>인천광역시 중구 영종대로196번길 15-25 반도유보라아파트 유토피아상가 2층</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>14</v>
+      </c>
+      <c r="R10" t="n">
+        <v>38</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>1764769256</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1764769256</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>카달로그인쇄</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>bizhows@naver.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>070-4556-6347</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>경기도 화성시 만세구 우정읍 국화리</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1540167300</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1540167300</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>광고대행</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>bizhows@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>070-4584-5861</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>인천광역시 중구 을왕동</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1253692395</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1253692395</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>팀스카이휘트니스</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>teamsky01@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>인천광역시 중구 신도시남로149번길 15 B1 팀스카이 휘트니스</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/teamsky01</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>96</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>121</v>
+      </c>
+      <c r="R13" t="n">
+        <v>217</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>1981200381</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1981200381</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>유티비티짐 24시</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>utbt_gym@naver.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0507-1335-6338</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>인천광역시 중구 흰바위로 228 비전프라자 9층 유티비티짐</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/utbt_gym</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>1282</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>271</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1553</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>1116960254</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1116960254</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>인터넷상거래</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>bizhows@naver.com</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>070-8904-2330</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>인천광역시 중구 을왕동</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>1317870361</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1317870361</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>광고대행</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>bizhows@naver.com</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>070-4594-4985</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>인천광역시 중구 무의동</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>1940611797</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1940611797</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>크로스핏 졸리 영종점</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>y00nji_0y@naver.com</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>인천광역시 중구 운중로 137-81 트레이닝 졸리</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://cafe.naver.com/jollymolly</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>8</v>
+      </c>
+      <c r="R17" t="n">
+        <v>8</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>2059999621</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2059999621</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>광고대행</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>bizhows@naver.com</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>070-4594-4466</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>인천광역시 중구 남북동</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>1280772559</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1280772559</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>인터넷상거래</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>bizhows@naver.com</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>070-5250-5311</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>경기도 화성시 만세구 우정읍 국화리</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>1093640347</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1093640347</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>퀸스짐 여성전용 헬스 PT 영종도점</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>queensgym@naver.com</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0507-1344-5829</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>인천광역시 중구 하늘별빛로65번길 8-21 303, 304호</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/queensgym</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>252</v>
+      </c>
+      <c r="R20" t="n">
+        <v>287</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>1471168773</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1471168773</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>투엔지 헬스PT</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>twongpt@naver.com</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0507-1471-2368</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>인천광역시 중구 하늘달빛로 76 동명프라자 10층 1002, 1003호</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/twongpt</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>195</v>
+      </c>
+      <c r="R21" t="n">
+        <v>237</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>1455820046</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1455820046</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>바디엣지랩</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>bodyedgelab@naver.com</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0507-1468-4861</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>인천광역시 중구 운서로7번길 37 1층</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bodyedgelab</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>274</v>
+      </c>
+      <c r="R22" t="n">
+        <v>280</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>1645436019</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1645436019</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>인터넷상거래</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>bizhows@naver.com</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>070-8904-3590</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>인천광역시 중구 남북동</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>1762400452</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1762400452</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>인터넷상거래</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>bizhows@naver.com</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>070-8904-1959</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>인천광역시 중구 운남동</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>1587781245</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1587781245</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>힙해짐 24시 헬스 PT 영종도점</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>kwon56231@naver.com</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0507-1439-0517</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>인천광역시 중구 하늘별빛로65번길 21 701, 702, 703, 704호</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>888</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>477</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1365</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>1731606747</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1731606747</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>더베럴피트니스 헬스PT 영종도점</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>thebetterfitness1@naver.com</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0507-1492-8972</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>인천광역시 중구 하늘중앙로225번길 3 7층, 8층</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://thebetterfitness.com</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>1003</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>579</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1582</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>1062429885</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1062429885</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>혁짐</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ahes0719@naver.com</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>0507-1311-1346</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>인천광역시 중구 넙디로 60 신원프라자 2층 혁짐</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_xdxbTJs</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>69</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>11</v>
+      </c>
+      <c r="R27" t="n">
+        <v>80</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>1591091774</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1591091774</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>이유피트니스</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2u2ufit@naver.com</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0507-1425-8052</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>인천광역시 중구 하늘별빛로 59 비젼프라자 3층 이유피트니스</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_Elxhxos</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>290</v>
+      </c>
+      <c r="R28" t="n">
+        <v>370</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>1957611417</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1957611417</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>찐피트니스 24시</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>zzin_fitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0507-1343-8596</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>인천광역시 중구 흰바위로 236 메가타워 10층</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/zzin_fitness</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>1245</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>484</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1729</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>1224879470</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1224879470</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>밸런스L.G.O휘트니스</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>topten0@naver.com</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>인천광역시 강화군 선원면 중앙로210번길 25</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>19399506</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/19399506</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>피트니스127</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>okfitness-daeshin@naver.com</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>0507-1370-1270</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>인천광역시 중구 흰바위로 262 럭키프라자 7층 피트니스127</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/fitness127_official</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>144</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>25</v>
+      </c>
+      <c r="R31" t="n">
+        <v>169</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>1650663436</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1650663436</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>에스오짐 1호점</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>topten0@naver.com</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>0507-1381-0814</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>인천광역시 강화군 강화읍 강화대로 199 2층</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>5</v>
+      </c>
+      <c r="R32" t="n">
+        <v>11</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>1342561169</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1342561169</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>스카이헬스클럽</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>rokmc9160@naver.com</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>0507-1468-7831</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>인천광역시 강화군 강화읍 관청길23번길 8 관청길23번길8 스카이헬스클럽</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>17</v>
+      </c>
+      <c r="R33" t="n">
+        <v>23</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>11847161</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/11847161</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>인터넷상거래</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>bizhows@naver.com</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>070-8904-1463</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>인천광역시 중구 무의동</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>1950964681</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1950964681</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>세탁소</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>수건세탁업체.세탁공장.미용실.헬스장.사우나.수건빨래.대량전문</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>total_clean_laundry@naver.com</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>070-4538-1567</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>경기도 안산시 단원구 풍도동</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>1282504501</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1282504501</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>크로스핏 영종</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>jmi87@naver.com</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0507-1349-0331</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>인천광역시 중구 신도시남로142번길 15 지하 1층 크로스핏영종</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/crossfit_yeong_jong</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>32</v>
+      </c>
+      <c r="R36" t="n">
+        <v>59</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>1602530898</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1602530898</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>체형스트레칭</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>bodybonelab@naver.com</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>032-752-6668</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>인천광역시 중구 신도시남로141번길 9</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>36019778</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/36019778</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>건호짐</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>cghtry@naver.com</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>인천광역시 중구 운남로 150 2층 203호</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/cghtry</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>48</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>332</v>
+      </c>
+      <c r="R38" t="n">
+        <v>380</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>1945757256</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1945757256</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>카달로그인쇄</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>bizhows@naver.com</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>070-4592-3860</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>경기도 안산시 단원구 대부남동</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>1915019681</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1915019681</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>우리동네 헬스/PT</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>subgymasan@naver.com</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>032-937-9870</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>인천광역시 강화군 불은면 강화동로 587 1층</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>1</v>
+      </c>
+      <c r="R40" t="n">
+        <v>15</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>2084651240</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2084651240</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>커브스 영종도클럽</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>curves1000@naver.com</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>0507-1304-4729</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>인천광역시 중구 하늘달빛로 70 영종 메디피아 702호</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/curves1000</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>97</v>
+      </c>
+      <c r="R41" t="n">
+        <v>98</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>1726060492</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1726060492</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>바디피티 대산점</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>y_0070@naver.com</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>0507-1437-8810</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>충청남도 서산시 대산읍 정자동1로 3 3층</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>1</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>2099342260</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2099342260</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>맥스휘트니스클럽. 맥스PT샵</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>on180102@naver.com</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>0507-1327-2830</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>인천광역시 강화군 강화읍 동문안길 9-1 4층</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>6</v>
+      </c>
+      <c r="R43" t="n">
+        <v>12</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>1506476586</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1506476586</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>머슬카페 운서역 2번출구점</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>musclecafe@naver.com</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>0507-1489-2060</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>인천광역시 중구 영종대로162번길 20 스타힐스 3층</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/muscle_cafe_2</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>74</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>7</v>
+      </c>
+      <c r="R44" t="n">
+        <v>81</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>1961270966</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1961270966</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>롯데케미칼사택휘트니스센터</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>bravemk130@naver.com</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>충청남도 서산시 대산읍 물안1로 123</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>65426906</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/65426906</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>몸짱휘트니스클럽</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>byy333@naver.com</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>0507-1419-9688</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>인천광역시 강화군 선원면 중앙로 154 2충</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/byy333</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>3</v>
+      </c>
+      <c r="R46" t="n">
+        <v>10</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>21494529</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/21494529</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>카달로그인쇄</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>bizhows@naver.com</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>070-4594-4955</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>인천광역시 중구 운남동</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>1077672927</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1077672927</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>에스오짐2호점</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>topten0@naver.com</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>032-934-2124</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>인천광역시 강화군 강화읍 중앙로 27 3층 S.O GYM 2호점</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://instagram.com/sogym_official2</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>139</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>12</v>
+      </c>
+      <c r="R48" t="n">
+        <v>151</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>1935773088</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1935773088</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>제이디엘마스터짐 1:1 PT</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>dudwhd8050@naver.com</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>032-746-9979</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>인천광역시 중구 신도시남로149번길 7 에어릴렉스 호텔 지하1층</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/dudwhd8050</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>286</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>980</v>
+      </c>
+      <c r="R49" t="n">
+        <v>1266</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>35581382</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/35581382</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>아라휘트니스</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>sfsnack2749@naver.com</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0507-1378-5860</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>인천광역시 중구 신도시남로141번길 5-8 천지인프라자 6층</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>http://instagram.com/ahra_pilates_unseo_neopdi</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>770</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>289</v>
+      </c>
+      <c r="R50" t="n">
+        <v>1059</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>1919453827</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1919453827</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>위너핏</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>boos66@naver.com</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0507-1476-1622</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>인천광역시 강화군 강화읍 남문로 14 3층</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/boos66</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>203</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>293</v>
+      </c>
+      <c r="R51" t="n">
+        <v>496</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>1895477243</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1895477243</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>맥스 PT&amp;GT</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>topten0@naver.com</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0507-1407-5359</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>인천광역시 강화군 강화읍 동문안길 9-1 4층</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>1</v>
+      </c>
+      <c r="R52" t="n">
+        <v>1</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>1296569152</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1296569152</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>제로벨스포츠</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>kmj1859@naver.com</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>0507-1320-9370</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>인천광역시 중구 하늘별빛로65번길 8-21 501호, 502호</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/zerobellsports5?igsh=MWw2eTYzbnIyNndmYw==</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>30</v>
+      </c>
+      <c r="R53" t="n">
+        <v>66</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>1413843645</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1413843645</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>더베럴캠프 그룹PT</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>thebetterfitness1@naver.com</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>0507-1440-8974</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>인천광역시 중구 하늘중앙로225번길 3 8층 803호</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/thebetterfitness1</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>151</v>
+      </c>
+      <c r="R54" t="n">
+        <v>177</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>1800815900</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1800815900</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>토크스퀘어</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>torquesquare@naver.com</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>인천광역시 중구 영종대로 94 9층 토크스퀘어</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/torquesquare</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
         <v>240</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="Q55" t="n">
         <v>671</v>
       </c>
-      <c r="R6" t="n">
+      <c r="R55" t="n">
         <v>911</v>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
         <is>
           <t>1814715870</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="U55" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1814715870</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>로이짐 PT 하늘도시점</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>vimeo2714@naver.com</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>032-721-5270</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>인천광역시 중구 하늘달빛로 80 203호</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>32</v>
+      </c>
+      <c r="R56" t="n">
+        <v>51</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>1105283785</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1105283785</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>LHU트레이닝센타</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>godnrdl1@naver.com</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>0507-1356-0219</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>인천광역시 중구 운남동로3번길 17 솔빌라 2층</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/godnrdl1</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>21</v>
+      </c>
+      <c r="R57" t="n">
+        <v>29</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>1648777064</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1648777064</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>요가,명상</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>하늘, 달요가</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>moonlightyoga@naver.com</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>0507-1470-5027</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>인천광역시 중구 하늘달빛로 94 502호</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/moonlightyoga</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>42</v>
+      </c>
+      <c r="R58" t="n">
+        <v>43</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>1067071740</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1067071740</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>읍사무소</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>대산읍커뮤니티센터</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>y_0070@naver.com</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>041-660-3736</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>충청남도 서산시 대산읍 수구물로 21 대산읍 커뮤니티센터</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>13</v>
+      </c>
+      <c r="R59" t="n">
+        <v>15</v>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>1098283835</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1098283835</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>탁구장</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>신공항탁구클럽</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>hangsangharu@naver.com</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>0507-1402-8537</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>인천광역시 중구 화랑목로100번길 31 1층 신공항탁구클럽</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/newairportpingpong/products/9828708841</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>3</v>
+      </c>
+      <c r="R60" t="n">
+        <v>4</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>641557502</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/641557502</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>태닝</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>더베럴태닝</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>thebetterfitness1@naver.com</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>인천광역시 중구 하늘중앙로225번길 3 701,801호</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/thebetter_fitness</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>4</v>
+      </c>
+      <c r="R61" t="n">
+        <v>11</v>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>1236952498</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1236952498</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>더베럴필라테스 영종하늘도시점</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>thebetterpilates1@naver.com</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>0507-1365-8910</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>인천광역시 중구 하늘중앙로225번길 3 8층</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/thebetterpilates1/223550411632</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>253</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>432</v>
+      </c>
+      <c r="R62" t="n">
+        <v>685</v>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>1161326068</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1161326068</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>그 숨 , 필라테스 영종하늘도시점</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>kjj260@naver.com</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>0507-1468-2802</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>인천광역시 중구 하늘달빛로 88 403호</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sum.pilates_</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>110</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>110</v>
+      </c>
+      <c r="R63" t="n">
+        <v>220</v>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>1928999654</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1928999654</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/옹진군_헬스장.xlsx
+++ b/naver-place-crawler/results_health/옹진군_헬스장.xlsx
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="Q2" t="n">
         <v>579</v>
       </c>
       <c r="R2" t="n">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -646,7 +646,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1244</v>
+        <v>1248</v>
       </c>
       <c r="Q3" t="n">
         <v>484</v>
       </c>
       <c r="R3" t="n">
-        <v>1728</v>
+        <v>1732</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="Q4" t="n">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="R4" t="n">
-        <v>1367</v>
+        <v>1370</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -903,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1282</v>
+        <v>1286</v>
       </c>
       <c r="Q5" t="n">
         <v>271</v>
       </c>
       <c r="R5" t="n">
-        <v>1553</v>
+        <v>1557</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
